--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3492,8 +3608,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:K18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3506,935 +3626,1048 @@
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아리랑 목동 — 민요채보-2/아리랑 목동.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">아리랑 목동</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">夾</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 洟</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃
 無</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">몽</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南
 無</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲
 南</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰
 洟</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 無
 潢</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="17"/>
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 夾</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" s="17"/>
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="17"/>
+      <c r="D5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">洟
 仲</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E5" s="17"/>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 黃</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">매</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="18"/>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="J6" s="13"/>
+      <c r="K6" s="18"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">洟</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">洟
 仲</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="15"/>
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">洟
 潢
 無</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 洟</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 南</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 洟</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">洟
 南</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="17"/>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢
 汰</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K8" s="17"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="17"/>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ○</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚
 △</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K10" s="18"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">洟</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 洟</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">洟
 潢
 仲</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">먹</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 夾</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="J14" s="13"/>
+      <c r="K14" s="18"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 無</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" s="17"/>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" s="17"/>
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 仲</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" s="17"/>
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 夾</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" s="18"/>
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 ○</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 △</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K18" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:K2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1214,13 +1214,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―|潢</t>
+          <t xml:space="preserve">汰|–|潢</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 潢</t>
         </is>
       </c>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1914,12 +1914,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I73" s="2"/>
@@ -3586,12 +3586,12 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I80" s="2"/>
@@ -3759,7 +3759,7 @@
       <c r="H4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―
+–
 潢</t>
         </is>
       </c>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G6" s="10"/>
@@ -4042,7 +4042,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C10" s="10"/>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
@@ -4068,13 +4068,13 @@
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="10"/>
@@ -4403,7 +4403,7 @@
       <c r="A17" s="0"/>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C17" s="9"/>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="F18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
@@ -4484,7 +4484,7 @@
       <c r="I18" s="10"/>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K18" s="10" t="inlineStr">

--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3659,69 +3697,69 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아리랑 목동</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">몽</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
@@ -3729,51 +3767,51 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">매</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –
 潢</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -3781,53 +3819,53 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아리</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">간에</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">까리</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3835,94 +3873,94 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 潢</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="27"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="I6" s="27"/>
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K6" s="10"/>
+      <c r="K6" s="27"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꺾</t>
         </is>
@@ -3930,53 +3968,53 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3984,55 +4022,55 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">래를</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃이</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -4040,93 +4078,93 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="27"/>
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
+      <c r="K10" s="27"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰리</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="H11" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K11" s="8" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -4134,52 +4172,52 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰리</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">먹</t>
         </is>
@@ -4187,53 +4225,53 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4241,55 +4279,55 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J14" s="17" t="inlineStr">
+      <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4297,52 +4335,52 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰리</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4350,50 +4388,50 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="C16" s="25"/>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰리</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
       </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4401,48 +4439,48 @@
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="C17" s="25"/>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="K17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4450,44 +4488,44 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="C18" s="27"/>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="I18" s="27"/>
+      <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K18" s="10" t="inlineStr">
+      <c r="K18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>

--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -3680,22 +3680,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3902,18 +3902,18 @@
       <c r="G6" s="27"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="27"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="K10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="82.06" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4386,11 +4386,11 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="82.06" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C16" s="25"/>
@@ -4437,7 +4437,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="82.06" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
@@ -4486,11 +4486,11 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="82.06" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C18" s="27"/>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I18" s="27"/>

--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -3837,7 +3837,8 @@
       </c>
       <c r="E5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리</t>
+          <t xml:space="preserve">아
+리</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -3847,7 +3848,8 @@
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">간에</t>
+          <t xml:space="preserve">간
+에</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -3857,7 +3859,8 @@
       </c>
       <c r="I5" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">까리</t>
+          <t xml:space="preserve">까
+리</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -4029,7 +4032,8 @@
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">래를</t>
+          <t xml:space="preserve">래
+를</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -4061,7 +4065,8 @@
       </c>
       <c r="I9" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">꽃이</t>
+          <t xml:space="preserve">꽃
+이</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -4136,7 +4141,8 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">쓰리</t>
+          <t xml:space="preserve">쓰
+리</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -4189,7 +4195,8 @@
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">쓰리</t>
+          <t xml:space="preserve">쓰
+리</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -4352,7 +4359,8 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">쓰리</t>
+          <t xml:space="preserve">쓰
+리</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -4401,7 +4409,8 @@
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">쓰리</t>
+          <t xml:space="preserve">쓰
+리</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">

--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +238,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3719,7 +3739,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3729,7 +3749,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3739,7 +3759,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">몽</t>
         </is>
@@ -3749,7 +3769,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3759,7 +3779,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
@@ -3772,13 +3792,13 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -3789,7 +3809,7 @@
 無</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">매</t>
         </is>
@@ -3801,7 +3821,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
@@ -3811,7 +3831,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K4" s="26" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -3824,7 +3844,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -3835,7 +3855,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 리</t>
@@ -3846,7 +3866,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">간
 에</t>
@@ -3857,7 +3877,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="I5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">까
 리</t>
@@ -3868,7 +3888,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="K5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3882,7 +3902,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -3892,7 +3912,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -3902,19 +3922,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="27"/>
+      <c r="I6" s="32"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K6" s="27"/>
+      <c r="K6" s="32"/>
     </row>
     <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
@@ -3923,7 +3943,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
@@ -3933,7 +3953,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -3943,7 +3963,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
@@ -3953,7 +3973,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -3963,7 +3983,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="K7" s="22" t="inlineStr">
+      <c r="K7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">꺾</t>
         </is>
@@ -3976,7 +3996,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -3986,7 +4006,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3997,7 +4017,7 @@
 無</t>
         </is>
       </c>
-      <c r="G8" s="25" t="inlineStr">
+      <c r="G8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
@@ -4007,7 +4027,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
@@ -4017,7 +4037,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K8" s="25" t="inlineStr">
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4030,7 +4050,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">래
 를</t>
@@ -4042,7 +4062,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4052,7 +4072,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G9" s="25" t="inlineStr">
+      <c r="G9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4063,7 +4083,7 @@
 無</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃
 이</t>
@@ -4075,7 +4095,7 @@
 無</t>
         </is>
       </c>
-      <c r="K9" s="25" t="inlineStr">
+      <c r="K9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -4088,13 +4108,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="27" t="inlineStr">
+      <c r="E10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4104,7 +4124,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="27" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -4114,13 +4134,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="27"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="27"/>
+      <c r="K10" s="32"/>
     </row>
     <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
@@ -4129,7 +4149,7 @@
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
@@ -4139,7 +4159,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰
 리</t>
@@ -4150,7 +4170,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -4160,7 +4180,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
@@ -4170,7 +4190,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K11" s="22" t="inlineStr">
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
@@ -4183,7 +4203,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
@@ -4193,7 +4213,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰
 리</t>
@@ -4204,7 +4224,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="25" t="inlineStr">
+      <c r="G12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4214,7 +4234,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4224,7 +4244,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K12" s="25" t="inlineStr">
+      <c r="K12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">먹</t>
         </is>
@@ -4238,7 +4258,7 @@
 無</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4248,7 +4268,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4258,7 +4278,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="25" t="inlineStr">
+      <c r="G13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
@@ -4268,7 +4288,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -4278,7 +4298,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K13" s="25" t="inlineStr">
+      <c r="K13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4291,7 +4311,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
@@ -4301,7 +4321,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4312,7 +4332,7 @@
 無</t>
         </is>
       </c>
-      <c r="G14" s="27" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -4323,7 +4343,7 @@
 無</t>
         </is>
       </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="I14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4334,7 +4354,7 @@
 無</t>
         </is>
       </c>
-      <c r="K14" s="27" t="inlineStr">
+      <c r="K14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -4347,7 +4367,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4357,7 +4377,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰
 리</t>
@@ -4368,7 +4388,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4378,7 +4398,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
@@ -4388,7 +4408,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K15" s="22" t="inlineStr">
+      <c r="K15" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4401,13 +4421,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰
 리</t>
@@ -4419,7 +4439,7 @@
 無</t>
         </is>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -4430,7 +4450,7 @@
 無</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
@@ -4440,7 +4460,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K16" s="25" t="inlineStr">
+      <c r="K16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4453,13 +4473,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C17" s="25"/>
+      <c r="C17" s="30"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E17" s="25" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4469,7 +4489,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G17" s="25" t="inlineStr">
+      <c r="G17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4479,7 +4499,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -4489,7 +4509,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K17" s="25" t="inlineStr">
+      <c r="K17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4502,13 +4522,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C18" s="27"/>
+      <c r="C18" s="32"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E18" s="27" t="inlineStr">
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4518,7 +4538,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G18" s="27" t="inlineStr">
+      <c r="G18" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
@@ -4528,13 +4548,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I18" s="27"/>
+      <c r="I18" s="32"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K18" s="27" t="inlineStr">
+      <c r="K18" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">야</t>
         </is>

--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -226,31 +221,16 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -359,7 +339,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
     </row>
@@ -423,7 +403,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">오른쪽 여백 제목 "아리랑 목동", 부제 "자진모리". 16정간 양식, 굵은 선 4칸마다. 번호 1~16을 정간마다 한 칸씩 쓴 양식(두 번호 한 칸 아님). 오른쪽 1~5줄만 사용(6·7·8줄 빈 칸이라 줄수 5). 각 율명 줄 바로 오른쪽 좁은 칸에 가사가 적혀 있어 그대로 전사함. 가사는 사용자 수기 채보 그대로 옮긴 것. 후렴(4줄)은 "아리아리동동 쓰리쓰리동동". 청성(潢汰 등)에 작은 연음선·요성 표시가 겹쳐 일부 둘째 율명 판독이 덜 확실함. AI 재판독.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간, 번호 1~16 정간마다 한 칸, 굵은 선 4칸마다) → 4/4·16. 오른쪽 1~5줄만 사용(6~8줄 빈 칸). 오른쪽 여백 제목 "아리랑 목동", 부제 "자진모리". 줄4는 후렴(아리아리동동 쓰리쓰리동동)으로 가사가 율명 줄 오른쪽 칸에 있음. 정간 대부분이 "율명|–율명" 2소박 구조. 줄1 8정간 가사 칸의 짧은 선은 생략.</t>
         </is>
       </c>
     </row>
@@ -648,26 +628,23 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|–無</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–無</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요성/작은 꾸밈 표시 있음</t>
-        </is>
-      </c>
+      <c r="J3" s="4"/>
       <c r="K3" s="2"/>
     </row>
     <row r="4">
@@ -693,12 +670,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–姑</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–姑</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +745,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -806,12 +784,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+–㴌</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -845,18 +824,18 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">들</t>
+          <t xml:space="preserve">들고</t>
         </is>
       </c>
       <c r="J8" s="4"/>
@@ -885,12 +864,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -998,12 +978,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+–㴌</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1037,13 +1018,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1116,12 +1097,13 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–無</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–無</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1155,17 +1137,18 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–姑</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–姑</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">씨</t>
+          <t xml:space="preserve">씨아</t>
         </is>
       </c>
       <c r="J16" s="4"/>
@@ -1194,19 +1177,16 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I17" s="2"/>
       <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
@@ -1272,14 +1252,13 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|–|潢</t>
+          <t xml:space="preserve">汰|–潢</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–
-潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1313,12 +1292,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰|–㴌</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰
+–㴌</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1426,12 +1406,13 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰|–㴌</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰
+–㴌</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -1465,13 +1446,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1505,12 +1486,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">·|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">·
+△</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1538,26 +1520,22 @@
       <c r="F26" s="2">
         <v>3</v>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">둘째 율명 흐림</t>
-        </is>
-      </c>
+      <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
     <row r="27">
@@ -1583,12 +1561,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1622,12 +1600,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+–㴌</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1661,13 +1640,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1701,12 +1680,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–潢</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–潢</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1740,13 +1720,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -1780,12 +1760,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1819,12 +1799,13 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I33" s="2"/>
@@ -1893,13 +1874,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1933,12 +1914,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+–㴌</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2007,12 +1989,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+–㴌</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2046,13 +2029,13 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2086,17 +2069,18 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–㴌</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–㴌</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">사자</t>
         </is>
       </c>
       <c r="J40" s="4"/>
@@ -2125,19 +2109,16 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I41" s="2"/>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
@@ -2164,12 +2145,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -2201,22 +2182,27 @@
       <c r="F43" s="2">
         <v>3</v>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|南</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="J43" s="4"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南 바로 위 짧은 가로선(연음으로 봄)</t>
+        </is>
+      </c>
       <c r="K43" s="2"/>
     </row>
     <row r="44">
@@ -2281,13 +2267,13 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2321,17 +2307,18 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–姑</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–姑</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">하</t>
+          <t xml:space="preserve">하오</t>
         </is>
       </c>
       <c r="J46" s="4"/>
@@ -2360,18 +2347,18 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">南|–南</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-無</t>
+          <t xml:space="preserve">南
+–南</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">오</t>
+          <t xml:space="preserve">리까</t>
         </is>
       </c>
       <c r="J47" s="4"/>
@@ -2400,19 +2387,15 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I48" s="2"/>
       <c r="J48" s="4"/>
       <c r="K48" s="2"/>
     </row>
@@ -2439,19 +2422,16 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">까</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I49" s="2"/>
       <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
@@ -2476,26 +2456,23 @@
       <c r="F50" s="2">
         <v>1</v>
       </c>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">후렴</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌|–㴌</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–㴌</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아리</t>
+        </is>
+      </c>
+      <c r="J50" s="4"/>
       <c r="K50" s="2"/>
     </row>
     <row r="51">
@@ -2521,17 +2498,18 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌|–㴌</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌
+–㴌</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">리</t>
+          <t xml:space="preserve">아리</t>
         </is>
       </c>
       <c r="J51" s="4"/>
@@ -2560,18 +2538,18 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|潢</t>
+          <t xml:space="preserve">汰|–潢</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아리</t>
+          <t xml:space="preserve">동</t>
         </is>
       </c>
       <c r="J52" s="4"/>
@@ -2639,17 +2617,18 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌|–㴌</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌
+–㴌</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">동</t>
+          <t xml:space="preserve">아리</t>
         </is>
       </c>
       <c r="J54" s="4"/>
@@ -2678,17 +2657,18 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌|–㴌</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌
+–㴌</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">아리</t>
         </is>
       </c>
       <c r="J55" s="4"/>
@@ -2717,18 +2697,18 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|潢</t>
+          <t xml:space="preserve">汰|–潢</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">리</t>
+          <t xml:space="preserve">동</t>
         </is>
       </c>
       <c r="J56" s="4"/>
@@ -2794,22 +2774,27 @@
       <c r="F58" s="2">
         <v>3</v>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑|–南</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–南</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰리</t>
         </is>
       </c>
-      <c r="J58" s="4"/>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">윗글자 변 없는 姑로 봄</t>
+        </is>
+      </c>
       <c r="K58" s="2"/>
     </row>
     <row r="59">
@@ -2835,12 +2820,13 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–南</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–南</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -2874,12 +2860,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+–無</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2952,12 +2939,13 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑|–南</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">姑
+–南</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2991,12 +2979,13 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–南</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–南</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3030,12 +3019,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+–無</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3145,18 +3135,23 @@
       <c r="F67" s="2">
         <v>1</v>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I67" s="2"/>
-      <c r="J67" s="4"/>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|南</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I67" s="3"/>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南 바로 위 짧은 가로선(연음으로 봄)</t>
+        </is>
+      </c>
       <c r="K67" s="2"/>
     </row>
     <row r="68">
@@ -3221,13 +3216,13 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|潢</t>
+          <t xml:space="preserve">南|–潢</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3261,12 +3256,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3300,12 +3295,13 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+–㴌</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3339,12 +3335,13 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+–無</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3378,12 +3375,13 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I73" s="2"/>
@@ -3413,12 +3411,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3452,12 +3450,13 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+–㴌</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3491,13 +3490,13 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3531,12 +3530,13 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南|–姑</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南
+–姑</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3607,18 +3607,22 @@
       <c r="F79" s="2">
         <v>4</v>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I79" s="2"/>
-      <c r="J79" s="4"/>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I79" s="3"/>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짧은 비스듬한 선, 점(·)일 수도</t>
+        </is>
+      </c>
       <c r="K79" s="2"/>
     </row>
     <row r="80">
@@ -3679,12 +3683,12 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I81" s="2"/>
@@ -3715,7 +3719,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="82.06" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3732,84 +3736,89 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="82.06" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–㴌</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+리</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">몽</t>
+        </is>
+      </c>
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">몽</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K3" s="28" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="82.06" customHeight="1">
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="C4" s="30"/>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="C4" s="24"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E4" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
+          <t xml:space="preserve">㴌
+–㴌</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+리</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="G4" s="30" t="inlineStr">
+–無</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">매</t>
         </is>
@@ -3817,34 +3826,34 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–
-潢</t>
-        </is>
-      </c>
-      <c r="I4" s="30" t="inlineStr">
+–潢</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="J4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–無</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="82.06" customHeight="1">
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -3852,205 +3861,216 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="E5" s="30" t="inlineStr">
+–潢</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–㴌</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">간
+에</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰
+–㴌</t>
+        </is>
+      </c>
+      <c r="I5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">까
+리</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–姑</t>
+        </is>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–潢</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">랑</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G6" s="26"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I6" s="26"/>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K6" s="26"/>
+    </row>
+    <row r="7" ht="52.21" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꽃</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌
+–㴌</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 리</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G5" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">간
-에</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–㴌</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">까
-리</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K5" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">지</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="82.06" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-潢</t>
-        </is>
-      </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E6" s="32" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I6" s="32"/>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K6" s="32"/>
-    </row>
-    <row r="7" ht="82.06" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C7" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꽃</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E7" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">생</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I7" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동</t>
-        </is>
-      </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="K7" s="28" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">꺾</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="82.06" customHeight="1">
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="inlineStr">
+          <t xml:space="preserve">潢
+–㴌</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="E8" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
+          <t xml:space="preserve">㴌
+–㴌</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아
+리</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="G8" s="30" t="inlineStr">
+–無</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="I8" s="30" t="inlineStr">
+          <t xml:space="preserve">汰
+–㴌</t>
+        </is>
+      </c>
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K8" s="30" t="inlineStr">
+          <t xml:space="preserve">潢
+–㴌</t>
+        </is>
+      </c>
+      <c r="K8" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="82.06" customHeight="1">
+    <row r="9" ht="52.21" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
+          <t xml:space="preserve">潢
+–無</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">래
 를</t>
@@ -4059,31 +4079,33 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-潢</t>
-        </is>
-      </c>
-      <c r="E9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
+–潢</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">南
+–㴌</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+자</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I9" s="30" t="inlineStr">
+–無</t>
+        </is>
+      </c>
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">꽃
 이</t>
@@ -4092,74 +4114,76 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">들</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="82.06" customHeight="1">
+–無</t>
+        </is>
+      </c>
+      <c r="K9" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">들
+고</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C10" s="32"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C10" s="26"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E10" s="32" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G10" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G10" s="26"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I10" s="32"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I10" s="26"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K10" s="32"/>
-    </row>
-    <row r="11" ht="82.06" customHeight="1">
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K10" s="26"/>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
-        </is>
-      </c>
-      <c r="C11" s="28" t="inlineStr">
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–南</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰
 리</t>
@@ -4167,20 +4191,20 @@
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G11" s="28" t="inlineStr">
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I11" s="29" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
@@ -4190,85 +4214,89 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="82.06" customHeight="1">
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="inlineStr">
+          <t xml:space="preserve">潢
+–㴌</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E12" s="30" t="inlineStr">
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰
 리</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K12" s="30" t="inlineStr">
+      <c r="K12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">먹</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="82.06" customHeight="1">
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
+–無</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E13" s="30" t="inlineStr">
+          <t xml:space="preserve">潢
+–無</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4278,50 +4306,53 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G13" s="30" t="inlineStr">
+      <c r="G13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">람</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I13" s="30" t="inlineStr">
+          <t xml:space="preserve">潢
+–㴌</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K13" s="30" t="inlineStr">
+          <t xml:space="preserve">潢
+–㴌</t>
+        </is>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="82.06" customHeight="1">
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南
+–姑</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">주</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">주</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4329,10 +4360,10 @@
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="G14" s="32" t="inlineStr">
+–無</t>
+        </is>
+      </c>
+      <c r="G14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -4340,10 +4371,10 @@
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I14" s="32" t="inlineStr">
+–無</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
@@ -4351,33 +4382,34 @@
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="K14" s="32" t="inlineStr">
+–無</t>
+        </is>
+      </c>
+      <c r="K14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="82.06" customHeight="1">
+    <row r="15" ht="52.21" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C15" s="28" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="inlineStr">
+          <t xml:space="preserve">姑
+–南</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰
 리</t>
@@ -4385,49 +4417,53 @@
       </c>
       <c r="F15" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南
+–姑</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하
+오</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
+–潢</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G15" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="I15" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">고</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K15" s="28" t="inlineStr">
+      <c r="K15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="82.06" customHeight="1">
+    <row r="16" ht="52.21" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C16" s="30"/>
+      <c r="C16" s="24"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="E16" s="30" t="inlineStr">
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">쓰
 리</t>
@@ -4435,51 +4471,54 @@
       </c>
       <c r="F16" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南
+–南</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">리
+까</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="G16" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">오</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="I16" s="30" t="inlineStr">
+–無</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K16" s="30" t="inlineStr">
+          <t xml:space="preserve">南
+–無</t>
+        </is>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="82.06" customHeight="1">
+    <row r="17" ht="52.21" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C17" s="30"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="E17" s="30" t="inlineStr">
+          <t xml:space="preserve">潢
+–無</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -4489,76 +4528,69 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G17" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리</t>
-        </is>
-      </c>
+      <c r="G17" s="25"/>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I17" s="30" t="inlineStr">
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
-        </is>
-      </c>
-      <c r="K17" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">씨</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="82.06" customHeight="1">
+          <t xml:space="preserve">南
+–姑</t>
+        </is>
+      </c>
+      <c r="K17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">씨
+아</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52.21" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C18" s="32"/>
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="C18" s="26"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G18" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">까</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="G18" s="26"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I18" s="32"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I18" s="26"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K18" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">야</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -403,7 +403,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간, 번호 1~16 정간마다 한 칸, 굵은 선 4칸마다) → 4/4·16. 오른쪽 1~5줄만 사용(6~8줄 빈 칸). 오른쪽 여백 제목 "아리랑 목동", 부제 "자진모리". 줄4는 후렴(아리아리동동 쓰리쓰리동동)으로 가사가 율명 줄 오른쪽 칸에 있음. 정간 대부분이 "율명|–율명" 2소박 구조. 줄1 8정간 가사 칸의 짧은 선은 생략.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간, 번호 1~16 정간마다 한 칸, 굵은 선 4칸마다) → 4/4·16. 오른쪽 1~5줄만 사용(6~8줄 빈 칸). 오른쪽 여백 제목 "아리랑 목동", 부제 "자진모리". 줄4는 후렴(아리아리동동 쓰리쓰리동동)으로 가사가 율명 줄 오른쪽 칸에 있음. 정간 대부분이 "율명|–율명" 2소박 구조. 줄1 8정간 가사 칸의 짧은 선은 생략. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -2069,13 +2069,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|–㴌</t>
+          <t xml:space="preserve">南|–姑</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-–㴌</t>
+–姑</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-–㴌</t>
+–姑</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">

--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -541,10 +541,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -487,17 +487,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -614,7 +614,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -668,6 +668,46 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3590,520 +3630,520 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:K18"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="57.14" customHeight="true">
+      <c r="B2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B3" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B4" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="20"/>
+      <c r="D4" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="21" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B5" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B6" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="7" t="s">
+      <c r="G6" s="22"/>
+      <c r="H6" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="22"/>
+      <c r="J6" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="12"/>
-    </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="K6" s="22"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B7" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B8" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B9" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="21" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="12"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="22"/>
+      <c r="D10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10" s="22"/>
+      <c r="H10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="22"/>
+      <c r="J10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="12"/>
-    </row>
-    <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="K10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B11" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="18" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B12" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="21" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B13" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="21" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B14" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="K14" s="22" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B15" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="18" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="9" t="s">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B16" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="21" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B17" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="7" t="s">
+      <c r="C17" s="21"/>
+      <c r="D17" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="G17" s="11"/>
-      <c r="H17" s="7" t="s">
+      <c r="G17" s="21"/>
+      <c r="H17" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="63.76" customHeight="true">
+      <c r="B18" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="22"/>
+      <c r="D18" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="7" t="s">
+      <c r="G18" s="22"/>
+      <c r="H18" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I18" s="12"/>
-      <c r="J18" s="7" t="s">
+      <c r="I18" s="22"/>
+      <c r="J18" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="K18" s="12"/>
+      <c r="K18" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4111,7 +4151,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="77" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="70"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/아리랑 목동.xlsx
+++ b/sheets/민요/검수/아리랑 목동.xlsx
@@ -3636,15 +3636,15 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="15" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="14" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="15" width="6"/>
   </cols>
   <sheetData>
